--- a/data/dividends_info_20260905.xlsx
+++ b/data/dividends_info_20260905.xlsx
@@ -663,8 +663,12 @@
           <t>IT0004587470</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
+      <c r="H5" t="n">
+        <v>0.5099999904632568</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.784313740156468</v>
+      </c>
       <c r="J5" t="n">
         <v>100</v>
       </c>
@@ -1035,8 +1039,12 @@
           <t>IT0004587470</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
+      <c r="H13" t="n">
+        <v>0.5099999904632568</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.784313740156468</v>
+      </c>
       <c r="J13" t="n">
         <v>44</v>
       </c>
@@ -1407,8 +1415,12 @@
           <t>IT0004587470</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
+      <c r="H21" t="n">
+        <v>0.5099999904632568</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.784313740156468</v>
+      </c>
       <c r="J21" t="n">
         <v>-12</v>
       </c>
@@ -1939,7 +1951,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>EQUITA GROUP S.p.A.</t>
+          <t>B&amp;C SPEAKERS S.p.A.</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1973,7 +1985,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>EL.EN. S.p.A.</t>
+          <t>EQUITA GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1990,7 +2002,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>CY4Gate S.p.A.</t>
+          <t>EL.EN. S.p.A.</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2007,7 +2019,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>BolognaFiere S.p.A.</t>
+          <t>CY4Gate S.p.A.</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2024,7 +2036,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>B&amp;C SPEAKERS S.p.A.</t>
+          <t>BolognaFiere S.p.A.</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2109,7 +2121,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
+          <t>Iniziative Bresciane - INBRE - S.p.A.</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2126,7 +2138,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Pharmanutra S.p.A.</t>
+          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2143,7 +2155,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Iniziative Bresciane - INBRE - S.p.A.</t>
+          <t>Pharmanutra S.p.A.</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2228,7 +2240,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Altea Green Power S.p.A.</t>
+          <t>IRCE s.p.a</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2238,14 +2250,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>IRCE s.p.a</t>
+          <t>Altea Green Power S.p.A.</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2255,14 +2267,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>NEWPRINCES</t>
+          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2279,7 +2291,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>NEWPRINCES</t>
+          <t>CIRCLE S.p.A.</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2289,14 +2301,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>I GRANDI VIAGGI S.p.A.</t>
+          <t>Gas Plus S.p.A.</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2306,14 +2318,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Sesa S.p.A.</t>
+          <t>Gas Plus S.p.A.</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2323,14 +2335,14 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Gas Plus S.p.A.</t>
+          <t>I GRANDI VIAGGI S.p.A.</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2340,14 +2352,14 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
+          <t>NEWPRINCES</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2364,7 +2376,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Gas Plus S.p.A.</t>
+          <t>NEWPRINCES</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2374,14 +2386,14 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>CIRCLE S.p.A.</t>
+          <t>Sesa S.p.A.</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2391,14 +2403,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Growens S.p.A.</t>
+          <t>S.S. Lazio S.p.A.</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2408,14 +2420,14 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>MB Annual Report</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>NEUROSOFT</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2425,14 +2437,14 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>NEUROSOFT</t>
+          <t>Sanlorenzo S.p.A.</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2442,14 +2454,14 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>S.S. Lazio S.p.A.</t>
+          <t>Growens S.p.A.</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2459,14 +2471,14 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>MB Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Sanlorenzo S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2483,7 +2495,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>MFE-MEDIAFOREUROPE N.V.</t>
+          <t>Somec S.p.A.</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2500,7 +2512,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Somec S.p.A.</t>
+          <t>Pattern S.p.A.</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2517,7 +2529,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Somec S.p.A.</t>
+          <t>MFE-MEDIAFOREUROPE N.V.</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2527,14 +2539,14 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Pattern S.p.A.</t>
+          <t>MFE-MEDIAFOREUROPE N.V.</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2544,14 +2556,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>Somec S.p.A.</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2619,7 +2631,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>MFE-MEDIAFOREUROPE N.V.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2789,7 +2801,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Confinvest Oro S.p.A.</t>
+          <t>I.CO.P. S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -2806,7 +2818,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>I.CO.P. S.p.A. Società Benefit</t>
+          <t>Confinvest Oro S.p.A.</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3027,7 +3039,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>ESI S.p.A.</t>
+          <t>ENTERA</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -3044,7 +3056,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>ENTERA</t>
+          <t>Directa SIM S.P.A.</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -3054,7 +3066,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -3071,14 +3083,14 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Directa SIM S.P.A.</t>
+          <t>CREACTIVES GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -3088,14 +3100,14 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>CREACTIVES GROUP S.p.A.</t>
+          <t>Friends S.p.A.</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -3105,14 +3117,14 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Friends S.p.A.</t>
+          <t>ESI S.p.A.</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -3129,7 +3141,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>POWERSOFT S.p.A.</t>
+          <t>RES S.p.A.</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -3146,7 +3158,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>rino petino S.p.A.</t>
+          <t>Sicily by Car S.p.A.</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -3163,7 +3175,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>eVISO S.p.A.</t>
+          <t>SIAV S.p.A.</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -3173,14 +3185,14 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
+          <t>POWERSOFT S.p.A.</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -3197,7 +3209,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Softlab S.p.A.</t>
+          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -3214,7 +3226,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Sicily by Car S.p.A.</t>
+          <t>eVISO S.p.A.</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -3224,14 +3236,14 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>RES S.p.A.</t>
+          <t>rino petino S.p.A.</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -3265,7 +3277,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>JUVENTUS F.C. S.p.A.</t>
+          <t>Softlab S.p.A.</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -3275,14 +3287,14 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>SIAV S.p.A.</t>
+          <t>JUVENTUS F.C. S.p.A.</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -3292,14 +3304,14 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Impianti S.p.A.</t>
+          <t>E-NOVIA S.p.A.</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -3316,7 +3328,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>BRIOSCHI SVILUPPO IMMOBILIARE S.p.A</t>
+          <t>Impianti S.p.A.</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -3333,7 +3345,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>DOTSTAY S.p.A.</t>
+          <t>Gismondi 1754 S.p.A.</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -3350,7 +3362,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>E-NOVIA S.p.A.</t>
+          <t>Giglio.com S.p.A.</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -3367,7 +3379,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>ELSA Solutions S.p.A.</t>
+          <t>Egomnia S.p.A.</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -3384,7 +3396,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>DIGITAL BROS S.p.A.</t>
+          <t>ELSA Solutions S.p.A.</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -3394,7 +3406,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3430,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Giglio.com S.p.A.</t>
+          <t>DOTSTAY S.p.A.</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -3435,7 +3447,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Gismondi 1754 S.p.A.</t>
+          <t>DIGITAL BROS S.p.A.</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -3445,14 +3457,14 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Egomnia S.p.A.</t>
+          <t>BRIOSCHI SVILUPPO IMMOBILIARE S.p.A</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -3469,7 +3481,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Allcore S.p.A.</t>
+          <t>Pasquarelli Auto S.p.A.</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -3486,7 +3498,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Smart Capital S.p.A.</t>
+          <t>BESTBE HOLDING S.p.A.</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -3503,7 +3515,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>BESTBE HOLDING S.p.A.</t>
+          <t>BASTOGI S.p.A.</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -3537,7 +3549,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>SBE-Varvit S.p.A.</t>
+          <t>MIT SIM S.p.A.</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -3554,7 +3566,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Predict S.p.A.</t>
+          <t>Maps S.p.A.</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -3571,7 +3583,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Maps S.p.A.</t>
+          <t>Allcore S.p.A.</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -3588,7 +3600,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>MIT SIM S.p.A.</t>
+          <t>gAIn360 S.p.A.</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -3605,7 +3617,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>ILPRA S.p.A.</t>
+          <t>Predict S.p.A.</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -3622,7 +3634,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>FOPE S.p.A.</t>
+          <t>Svas Biosana S.p.A.</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -3639,7 +3651,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Ecomembrane S.p.A.</t>
+          <t>Smart Capital S.p.A.</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -3656,7 +3668,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>ESAUTOMOTION S.p.A.</t>
+          <t>SIAV S.p.A.</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -3666,14 +3678,14 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>DANIELI &amp; C. S.p.A.</t>
+          <t>ILPRA S.p.A.</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -3683,14 +3695,14 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Pasquarelli Auto S.p.A.</t>
+          <t>FOPE S.p.A.</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -3707,7 +3719,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>SIAV S.p.A.</t>
+          <t>Ecomembrane S.p.A.</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -3717,14 +3729,14 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Svas Biosana S.p.A.</t>
+          <t>ESAUTOMOTION S.p.A.</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -3741,7 +3753,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>BASTOGI S.p.A.</t>
+          <t>DANIELI &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -3751,14 +3763,14 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>VINEXT S.p.A.</t>
+          <t>SBE-Varvit S.p.A.</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -3775,7 +3787,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>gAIn360 S.p.A.</t>
+          <t>VINEXT S.p.A.</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -3792,7 +3804,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>T.P.S. S.p.A.</t>
+          <t>Guidotti Ships S.p.A.</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -3809,7 +3821,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Simone S.p.A.</t>
+          <t>Farmacosmo S.p.A.</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -3826,7 +3838,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Redelfi S.p.A.</t>
+          <t>FRENDY ENERGY S.p.A.</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -3843,7 +3855,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Radici Pietro Industries &amp; Brands S.p.A.</t>
+          <t>Estrima S.p.A.</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -3860,7 +3872,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>PREMIA FINANCE S.P.A</t>
+          <t>Energy S.p.A.</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -3877,7 +3889,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>OMER S.p.A.</t>
+          <t>T.P.S. S.p.A.</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -3894,7 +3906,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Estrima S.p.A.</t>
+          <t>YOLO GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -3911,7 +3923,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>YOLO GROUP S.p.A.</t>
+          <t>ZEST S.p.A.</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -3928,7 +3940,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>TMP Group S.p.A.</t>
+          <t>OMER S.p.A.</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -3945,7 +3957,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Triboo S.p.A.</t>
+          <t>PREMIA FINANCE S.P.A</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -3962,7 +3974,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Ambromobiliare S.p.A.</t>
+          <t>Radici Pietro Industries &amp; Brands S.p.A.</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -3979,7 +3991,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>AEFFE S.p.A.</t>
+          <t>Redelfi S.p.A.</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -3989,14 +4001,14 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>AEFFE S.p.A.</t>
+          <t>Simone S.p.A.</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -4006,14 +4018,14 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A.B.P. Nocivelli S.p.A.</t>
+          <t>TMP Group S.p.A.</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -4023,14 +4035,14 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A.B.P. Nocivelli S.p.A.</t>
+          <t>Tecno S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -4040,14 +4052,14 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>ZEST S.p.A.</t>
+          <t>Telmes S.p.A.</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -4064,7 +4076,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Guidotti Ships S.p.A.</t>
+          <t>TradeLab S.p.A.</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -4081,7 +4093,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Energy S.p.A.</t>
+          <t>Triboo S.p.A.</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -4098,7 +4110,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>FRENDY ENERGY S.p.A.</t>
+          <t>Edil San Felice S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -4115,7 +4127,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Markbass S.p.A.</t>
+          <t>CIRCLE S.p.A.</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -4132,7 +4144,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Farmacosmo S.p.A.</t>
+          <t>EDILIZIACROBATICA S.p.A.</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -4142,14 +4154,14 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Metriks AI S.p.A. Società Benefit</t>
+          <t>Ambromobiliare S.p.A.</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -4166,7 +4178,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Next Geosolutions Europe S.p.A.</t>
+          <t>AEFFE S.p.A.</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -4176,14 +4188,14 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Nusco S.p.A.</t>
+          <t>AEFFE S.p.A.</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -4193,14 +4205,14 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>CIRCLE S.p.A.</t>
+          <t>A.B.P. Nocivelli S.p.A.</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -4210,14 +4222,14 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>DBA GROUP S.p.A.</t>
+          <t>A.B.P. Nocivelli S.p.A.</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -4227,14 +4239,14 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>EDILIZIACROBATICA S.p.A.</t>
+          <t>Nusco S.p.A.</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -4244,14 +4256,14 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Edil San Felice S.p.A. Società Benefit</t>
+          <t>Metriks AI S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -4261,14 +4273,14 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>MARZOCCHI POMPE S.p.A.</t>
+          <t>Markbass S.p.A.</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -4285,7 +4297,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Longino &amp; Cardenal S.p.A.</t>
+          <t>MARZOCCHI POMPE S.p.A.</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -4319,7 +4331,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>INNOVATEC S.p.A.</t>
+          <t>Longino &amp; Cardenal S.p.A.</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -4336,7 +4348,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Haiki+ S.p.A.</t>
+          <t>Next Geosolutions Europe S.p.A.</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -4353,7 +4365,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>TradeLab S.p.A.</t>
+          <t>INNOVATEC S.p.A.</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -4370,7 +4382,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Telmes S.p.A.</t>
+          <t>Haiki+ S.p.A.</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -4387,7 +4399,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Tecno S.p.A. Società Benefit</t>
+          <t>DBA GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -4414,7 +4426,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -4438,7 +4450,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Franchi Umberto Marmi S.p.A.</t>
+          <t>Seri Industrial S.p.A.</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -4455,7 +4467,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>First Capital S.p.A.</t>
+          <t>Saccheria F.lli Franceschetti S.p.A.</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -4472,7 +4484,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>PLANETEL S.p.A.</t>
+          <t>SOSTRAVEL.COM S.p.A.</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -4489,7 +4501,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Otofarma S.p.A.</t>
+          <t>SOGES GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -4506,7 +4518,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>OPS Italia S.p.A.</t>
+          <t>COFLE S.p.A.</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -4523,7 +4535,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>FIDIA S.p.A</t>
+          <t>Bellini Nautica S.p.A.</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -4540,7 +4552,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>FAE Technology Società Benefit S.p.A.</t>
+          <t>BORGOSESIA S.p.A.</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -4557,7 +4569,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>ErreDue S.p.A.</t>
+          <t>Arterra Bioscience S.p.A.</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -4574,7 +4586,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>ATON Green Storage S.p.A.</t>
+          <t>Adventure S.p.A.</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -4591,7 +4603,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Bellini Nautica S.p.A.</t>
+          <t>ATON Green Storage S.p.A.</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -4608,7 +4620,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Alfio Bardolla Training Group S.p.A.</t>
+          <t>OPS Italia S.p.A.</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -4625,7 +4637,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Energy Time S.p.A.</t>
+          <t>Otofarma S.p.A.</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -4642,7 +4654,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Magis S.p.A.</t>
+          <t>PLANETEL S.p.A.</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -4659,7 +4671,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Misitano &amp; Stracuzzi S.p.A.</t>
+          <t>Rocket Sharing Company S.p.A.</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -4676,7 +4688,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Monnalisa S.p.A.</t>
+          <t>Novamarine S.p.A.</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -4693,7 +4705,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>NOTORIOUS PICTURES S.p.A.</t>
+          <t>Riba Mundo Tecnologia S.A.</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -4710,7 +4722,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Novamarine S.p.A.</t>
+          <t>Racing Force S.p.A.</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -4727,7 +4739,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>International Care Company S.p.A.</t>
+          <t>Alfio Bardolla Training Group S.p.A.</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -4744,7 +4756,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>ISCC FINTECH S.p.A.</t>
+          <t>NOTORIOUS PICTURES S.p.A.</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -4761,7 +4773,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Adventure S.p.A.</t>
+          <t>EPH INVEST S.p.A.</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -4778,7 +4790,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>HIGH QUALITY FOOD S.p.A.</t>
+          <t>Misitano &amp; Stracuzzi S.p.A.</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -4795,7 +4807,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Gens Aurea S.p.A.</t>
+          <t>EDILIZIACROBATICA S.p.A.</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -4812,7 +4824,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Gambero Rosso S.p.A.</t>
+          <t>E.T.S. S.p.A. Engineering and Technical Services</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -4829,7 +4841,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>GREEN OLEO S.p.A</t>
+          <t>Distribuzione Elettrica Adriatica S.p.A.</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -4846,7 +4858,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>GPI S.p.A.</t>
+          <t>Datrix S.p.A.</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -4863,7 +4875,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>GEL S.p.A.</t>
+          <t>Copernico SIM S.p.A.</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -4880,7 +4892,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>COFLE S.p.A.</t>
+          <t>CSP INTERNATIONAL FASHION GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -4897,7 +4909,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>BORGOSESIA S.p.A.</t>
+          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -4914,7 +4926,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>Arterra Bioscience S.p.A.</t>
+          <t>COMPAGNIA DEI CARAIBI S.p.A.</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -4931,7 +4943,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>Grifal S.p.A.</t>
+          <t>Franchi Umberto Marmi S.p.A.</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -4948,7 +4960,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Lemon Sistemi S.p.A.</t>
+          <t>First Capital S.p.A.</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -4965,7 +4977,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>Energy S.p.A.</t>
+          <t>FIDIA S.p.A</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -4975,14 +4987,14 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>ETI S.p.A.</t>
+          <t>FAE Technology Società Benefit S.p.A.</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -4999,7 +5011,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Saccheria F.lli Franceschetti S.p.A.</t>
+          <t>ErreDue S.p.A.</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -5016,7 +5028,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>SOSTRAVEL.COM S.p.A.</t>
+          <t>Energy Time S.p.A.</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -5033,7 +5045,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>SOGES GROUP S.p.A.</t>
+          <t>Energy S.p.A.</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -5043,14 +5055,14 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>Rocket Sharing Company S.p.A.</t>
+          <t>EUKEDOS S.p.A.</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -5067,7 +5079,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>Riba Mundo Tecnologia S.A.</t>
+          <t>ETI S.p.A.</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -5084,7 +5096,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>iVision Tech S.p.A.</t>
+          <t>TESSELLIS S.p.A.</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -5101,7 +5113,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
+          <t>Magis S.p.A.</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -5111,14 +5123,14 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>EUKEDOS S.p.A.</t>
+          <t>Monnalisa S.p.A.</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -5135,7 +5147,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>Racing Force S.p.A.</t>
+          <t>Telesia S.p.A.</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -5152,7 +5164,7 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>ENA S.p.A.</t>
+          <t>Reti S.p.A.</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -5169,7 +5181,7 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>EDILIZIACROBATICA S.p.A.</t>
+          <t>HIGH QUALITY FOOD S.p.A.</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -5179,7 +5191,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
@@ -5196,14 +5208,14 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>E.T.S. S.p.A. Engineering and Technical Services</t>
+          <t>Vimi Fasteners S.p.A.</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -5220,7 +5232,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>Distribuzione Elettrica Adriatica S.p.A.</t>
+          <t>UCapital24 S.p.A.</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -5237,7 +5249,7 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>Datrix S.p.A.</t>
+          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -5247,14 +5259,14 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>Copernico SIM S.p.A.</t>
+          <t>iVision Tech S.p.A.</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -5271,7 +5283,7 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>CSP INTERNATIONAL FASHION GROUP S.p.A.</t>
+          <t>GEL S.p.A.</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -5288,7 +5300,7 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
+          <t>GPI S.p.A.</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -5305,7 +5317,7 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>COMPAGNIA DEI CARAIBI S.p.A.</t>
+          <t>GREEN OLEO S.p.A</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -5322,7 +5334,7 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>Seri Industrial S.p.A.</t>
+          <t>Gambero Rosso S.p.A.</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -5339,7 +5351,7 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>TESSELLIS S.p.A.</t>
+          <t>Gens Aurea S.p.A.</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -5356,7 +5368,7 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>Reti S.p.A.</t>
+          <t>Grifal S.p.A.</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -5373,7 +5385,7 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>UCapital24 S.p.A.</t>
+          <t>ISCC FINTECH S.p.A.</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -5390,7 +5402,7 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>EPH INVEST S.p.A.</t>
+          <t>International Care Company S.p.A.</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -5407,7 +5419,7 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>Vimi Fasteners S.p.A.</t>
+          <t>Lemon Sistemi S.p.A.</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -5424,7 +5436,7 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>Telesia S.p.A.</t>
+          <t>ENA S.p.A.</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -5441,7 +5453,7 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>doxee S.p.A.</t>
+          <t>IDNTT S.A.</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -5458,7 +5470,7 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>EXPERT.AI S.p.A.</t>
+          <t>Vivenda Group S.p.A.</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -5475,7 +5487,7 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>EdgeLab S.p.A.</t>
+          <t>Vantea Smart S.p.A.</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -5492,7 +5504,7 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>Emma Villas S.p.A.</t>
+          <t>Valica S.p.A.</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -5509,7 +5521,7 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>Energy Time S.p.A.</t>
+          <t>VNE S.p.A.</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -5519,14 +5531,14 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>Eprcomunicazione S.p.A. Società Benefit</t>
+          <t>The Italian Sea Group S.p.A.</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -5536,14 +5548,14 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>Execus S.p.A.</t>
+          <t>Tenax International S.p.A.</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -5560,7 +5572,7 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>Finanza.tech S.p.A. Società Benefit</t>
+          <t>TRAWELL CO S.p.A.</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -5577,7 +5589,7 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>First Point S.p.A.</t>
+          <t>CleanBnB S.p.A.</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -5594,7 +5606,7 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>G.M. Leather S.p.A.</t>
+          <t>Casta Diva Group S.p.A.</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -5611,7 +5623,7 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>Cogefeed S.p.A.</t>
+          <t>CLASS EDITORI S.p.A.</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -5628,7 +5640,7 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>MONDO TV S.p.A.</t>
+          <t>B.F. S.p.A.</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -5645,7 +5657,7 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>Matica Fintec S.p.A.</t>
+          <t>Alia Mentis S.p.A.</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -5662,7 +5674,7 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>FRANCHETTI S.p.A.</t>
+          <t>Cogefeed S.p.A.</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -5679,7 +5691,7 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>Vivenda Group S.p.A.</t>
+          <t>Com.Tel S.p.A.</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -5696,7 +5708,7 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>MEVIM S.p.A.</t>
+          <t>doxee S.p.A.</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -5713,7 +5725,7 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>Vantea Smart S.p.A.</t>
+          <t>Cube Labs S.p.A.</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -5730,7 +5742,7 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>ESPE S.p.A.</t>
+          <t>DESTINATION ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -5747,7 +5759,7 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>ECOSUNTEK S.p.A.</t>
+          <t>Dedem S.p.A.</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -5764,7 +5776,7 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>E-Globe S.p.A.</t>
+          <t>Dipietro Group S.p.A.</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -5781,7 +5793,7 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>Dipietro Group S.p.A.</t>
+          <t>E-Globe S.p.A.</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -5798,7 +5810,7 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>Dedem S.p.A.</t>
+          <t>ECOSUNTEK S.p.A.</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -5815,7 +5827,7 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>DESTINATION ITALIA S.p.A.</t>
+          <t>ESPE S.p.A.</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -5832,7 +5844,7 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>Met.Extra Group S.p.A.</t>
+          <t>ACQUAZZURRA S.p.A.</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -5849,7 +5861,7 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>DEODATO.GALLERY S.p.A.</t>
+          <t>ABC Company S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -5866,7 +5878,7 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>Com.Tel S.p.A.</t>
+          <t>AATECH S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -5883,7 +5895,7 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>TRAWELL CO S.p.A.</t>
+          <t>Racing Force S.p.A.</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -5893,14 +5905,14 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>Tenax International S.p.A.</t>
+          <t>RedFish LongTerm Capital S.p.A.</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -5917,7 +5929,7 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>The Italian Sea Group S.p.A.</t>
+          <t>Solid World Group S.p.A.</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -5927,14 +5939,14 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>VNE S.p.A.</t>
+          <t>Società Editoriale il Fatto S.p.A.</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -5951,7 +5963,7 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>Valica S.p.A.</t>
+          <t>SG COMPANY SOCIETÀ BENEFIT S.p.A.</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -5968,7 +5980,7 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>Cube Labs S.p.A.</t>
+          <t>DEODATO.GALLERY S.p.A.</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -5985,7 +5997,7 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>OPS ECOM S.p.A.</t>
+          <t>HELYX INDUSTRIES S.p.A.</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -5995,14 +6007,14 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>OPT S.p.A.</t>
+          <t>ROSETTI MARINO S.p.A.</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -6019,7 +6031,7 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>Officina Stellare S.p.A.</t>
+          <t>Pozzi Milano S.p.A.</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -6036,7 +6048,7 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>ACQUAZZURRA S.p.A.</t>
+          <t>Piu' Medical S.p.A.</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -6053,7 +6065,7 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>Alia Mentis S.p.A.</t>
+          <t>Portobello S.p.A.</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -6070,7 +6082,7 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>B.F. S.p.A.</t>
+          <t>EXPERT.AI S.p.A.</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -6087,7 +6099,7 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>CLASS EDITORI S.p.A.</t>
+          <t>EdgeLab S.p.A.</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -6104,7 +6116,7 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>Casta Diva Group S.p.A.</t>
+          <t>Emma Villas S.p.A.</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -6121,7 +6133,7 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>CleanBnB S.p.A.</t>
+          <t>Energy Time S.p.A.</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -6131,14 +6143,14 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>ABC Company S.p.A. Società Benefit</t>
+          <t>PROMOTICA S.p.A.</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -6155,7 +6167,7 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>Gentili Mosconi S.p.A.</t>
+          <t>Eprcomunicazione S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -6172,7 +6184,7 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>IDNTT S.A.</t>
+          <t>MEVIM S.p.A.</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -6189,7 +6201,7 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>Itway S.p.A.</t>
+          <t>Lucisano Media Group S.p.A.</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -6206,7 +6218,7 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>KALEON S.P.A.</t>
+          <t>Litix S.p.A.</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -6240,7 +6252,7 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>Litix S.p.A.</t>
+          <t>KALEON S.P.A.</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -6257,7 +6269,7 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>MONDO TV FRANCE</t>
+          <t>Itway S.p.A.</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -6274,7 +6286,7 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>HELYX INDUSTRIES S.p.A.</t>
+          <t>MONDO TV FRANCE</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -6291,7 +6303,7 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>AATECH S.p.A. Società Benefit</t>
+          <t>PLC S.p.A.</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -6308,7 +6320,7 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>Portobello S.p.A.</t>
+          <t>Officina Stellare S.p.A.</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -6325,7 +6337,7 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>Piu' Medical S.p.A.</t>
+          <t>OPT S.p.A.</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -6342,7 +6354,7 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>PLC S.p.A.</t>
+          <t>G.M. Leather S.p.A.</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -6359,7 +6371,7 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>Solid World Group S.p.A.</t>
+          <t>First Point S.p.A.</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -6376,7 +6388,7 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>Società Editoriale il Fatto S.p.A.</t>
+          <t>Finanza.tech S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -6393,7 +6405,7 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>SG COMPANY SOCIETÀ BENEFIT S.p.A.</t>
+          <t>Praexidia Industrie Strategiche S.p.A.</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -6410,7 +6422,7 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>Reway Group S.p.A.</t>
+          <t>FRANCHETTI S.p.A.</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -6427,7 +6439,7 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>Lucisano Media Group S.p.A.</t>
+          <t>Renovalo S.p.A.</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -6444,7 +6456,7 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>Renovalo S.p.A.</t>
+          <t>Gentili Mosconi S.p.A.</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -6461,7 +6473,7 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>ROSETTI MARINO S.p.A.</t>
+          <t>MONDO TV S.p.A.</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -6478,7 +6490,7 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>Praexidia Industrie Strategiche S.p.A.</t>
+          <t>Matica Fintec S.p.A.</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -6495,7 +6507,7 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>Pozzi Milano S.p.A.</t>
+          <t>Met.Extra Group S.p.A.</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -6512,7 +6524,7 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>PROMOTICA S.p.A.</t>
+          <t>OPS ECOM S.p.A.</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -6522,14 +6534,14 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>RedFish LongTerm Capital S.p.A.</t>
+          <t>Execus S.p.A.</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -6546,7 +6558,7 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>Racing Force S.p.A.</t>
+          <t>Reway Group S.p.A.</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -6556,14 +6568,14 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>Renovalo S.p.A.</t>
+          <t>S.S. Lazio S.p.A.</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -6573,14 +6585,14 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>SB Annual Report</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>S.S. Lazio S.p.A.</t>
+          <t>LANDI RENZO S.p.A.</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -6590,14 +6602,14 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>SB Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>LANDI RENZO S.p.A.</t>
+          <t>Renovalo S.p.A.</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
@@ -6607,7 +6619,7 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -6652,44 +6664,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>CleanBnB S.p.A.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>